--- a/docs/architecture/v2-m6b-golden-workings.xlsx
+++ b/docs/architecture/v2-m6b-golden-workings.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -482,7 +482,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Each phase's control statuses are derived from the scenario's facts and each step's state from an independent implementation of the DEC-069 rules (order, sign-offs, lapses), then compared with the hand-written expectations. The platform's API test matches the same states exactly.</t>
+          <t>Each phase's control statuses are derived from the scenario's facts and each step's state from an independent implementation of the DEC-069 rules as amended by DEC-070 (order, sign-offs, lapses; steps 12 to 14 through their own records), then compared with the hand-written expectations. The platform's API test matches the same states exactly.</t>
         </is>
       </c>
     </row>
@@ -528,6 +528,16 @@
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>lapse: Phase 5: a draft bill dated 15.12.2026 makes step 1's control need attention again; its sign-off lapses. Steps 2 to 11 keep their own controls and stay DONE. Step 9 reopened: its dependency (step 1) is not DONE, so it is BLOCKED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Revision: 2026-10-21, V2-M6c (DEC-070): steps 12 to 14 are no longer LATER. Step 12 (partner review) depends on steps 1 to 11, and its control is READY because the accounts document is complete: TODO in phase 4, BLOCKED otherwise. Step 13 (client approval) needs attention: no live partner review, the 2026 period is open and the approval facts are not set. Step 14 (the package) needs attention: no client approval. Both are BLOCKED. Signing off step 12 through the workflow is refused as step_own_record (was step_later). Steps 1 to 11 and the current step of every phase are unchanged. The V2-M6b acceptance evidence at 9868fbc stands as recorded.</t>
         </is>
       </c>
     </row>
@@ -711,17 +721,17 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>- / LATER</t>
+          <t>READY / BLOCKED</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>- / LATER</t>
+          <t>ATTENTION / BLOCKED</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>- / LATER</t>
+          <t>ATTENTION / BLOCKED</t>
         </is>
       </c>
     </row>
@@ -791,17 +801,17 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>- / LATER</t>
+          <t>READY / BLOCKED</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>- / LATER</t>
+          <t>ATTENTION / BLOCKED</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>- / LATER</t>
+          <t>ATTENTION / BLOCKED</t>
         </is>
       </c>
     </row>
@@ -871,17 +881,17 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>- / LATER</t>
+          <t>READY / BLOCKED</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>- / LATER</t>
+          <t>ATTENTION / BLOCKED</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>- / LATER</t>
+          <t>ATTENTION / BLOCKED</t>
         </is>
       </c>
     </row>
@@ -951,17 +961,17 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>- / LATER</t>
+          <t>READY / TODO</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>- / LATER</t>
+          <t>ATTENTION / BLOCKED</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>- / LATER</t>
+          <t>ATTENTION / BLOCKED</t>
         </is>
       </c>
     </row>
@@ -1031,17 +1041,17 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>- / LATER</t>
+          <t>READY / BLOCKED</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>- / LATER</t>
+          <t>ATTENTION / BLOCKED</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>- / LATER</t>
+          <t>ATTENTION / BLOCKED</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1413,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["READY", "BLOCKED"]</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["READY", "BLOCKED"]</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1430,12 +1440,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1457,12 +1467,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1808,12 +1818,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["READY", "BLOCKED"]</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["READY", "BLOCKED"]</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1835,12 +1845,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1862,12 +1872,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -2267,12 +2277,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["READY", "BLOCKED"]</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["READY", "BLOCKED"]</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -2294,12 +2304,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -2321,12 +2331,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -2672,12 +2682,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["READY", "TODO"]</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["READY", "TODO"]</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -2699,12 +2709,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -2726,12 +2736,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -2780,12 +2790,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>"step_later"</t>
+          <t>"step_own_record"</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>"step_later"</t>
+          <t>"step_own_record"</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -3104,12 +3114,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["READY", "BLOCKED"]</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["READY", "BLOCKED"]</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -3131,12 +3141,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -3158,12 +3168,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>[null, "LATER"]</t>
+          <t>["ATTENTION", "BLOCKED"]</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
